--- a/Documents/TAN measurements compilation.xlsx
+++ b/Documents/TAN measurements compilation.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC229295-AEE3-4F17-92E6-450F99C9CED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84BB5EC-E576-4ECE-BEF4-8CB404BC12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TAN" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,6 +36,20 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>Samples</t>
+  </si>
+  <si>
+    <t>Sample Date</t>
+  </si>
+  <si>
+    <t>TAN</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +83,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,9 +420,152 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7D8B01-72EE-4FF7-992E-EE322EDC7DFE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C2">
+        <v>58.756</v>
+      </c>
+      <c r="D2">
+        <v>60.198399999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C3" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C4">
+        <v>65.340559999999996</v>
+      </c>
+      <c r="D4">
+        <v>62.852820000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46286</v>
+      </c>
+      <c r="C6">
+        <v>70.827500000000001</v>
+      </c>
+      <c r="D6">
+        <v>72.215599999999995</v>
+      </c>
+      <c r="E6">
+        <v>63.066099999999999</v>
+      </c>
+      <c r="F6">
+        <v>63.582700000000003</v>
+      </c>
+      <c r="G6">
+        <v>63.283499999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C7" s="1">
+        <v>46290</v>
+      </c>
+      <c r="E7" s="1">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46289</v>
+      </c>
+      <c r="C8">
+        <v>68.692300000000003</v>
+      </c>
+      <c r="D8">
+        <v>70.171400000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C9" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46290</v>
+      </c>
+      <c r="C10">
+        <v>59.997399999999999</v>
+      </c>
+      <c r="D10">
+        <v>58.849600000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C11" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46283</v>
+      </c>
+      <c r="C12">
+        <v>77.072999999999993</v>
+      </c>
+      <c r="D12">
+        <v>77.333600000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C13" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Documents/TAN measurements compilation.xlsx
+++ b/Documents/TAN measurements compilation.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84BB5EC-E576-4ECE-BEF4-8CB404BC12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FCE73B-E87A-451D-927E-0D60D81DACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
+    <sheet name="Timesheet" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Samples</t>
   </si>
@@ -48,6 +49,18 @@
   </si>
   <si>
     <t>TAN</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>100% water stripping for pyoil</t>
+  </si>
+  <si>
+    <t>0% water stripping for pyoil</t>
   </si>
 </sst>
 </file>
@@ -568,4 +581,49 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E27DB59-CC7B-4BA0-B3F8-3C1105C01C74}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/TAN measurements compilation.xlsx
+++ b/Documents/TAN measurements compilation.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FCE73B-E87A-451D-927E-0D60D81DACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ACD576-F557-4362-925C-DF0E1113E997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
-    <sheet name="Timesheet" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Timesheet" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Samples</t>
   </si>
@@ -61,6 +62,12 @@
   </si>
   <si>
     <t>0% water stripping for pyoil</t>
+  </si>
+  <si>
+    <t>50% water stripping for pyoil</t>
+  </si>
+  <si>
+    <t>sample</t>
   </si>
 </sst>
 </file>
@@ -96,9 +103,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -584,8 +592,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB39E3B-1647-40FA-8E29-C72F98988571}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C2">
+        <v>58.756</v>
+      </c>
+      <c r="D2">
+        <v>60.198399999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>65.340559999999996</v>
+      </c>
+      <c r="D3">
+        <v>62.852820000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>70.827500000000001</v>
+      </c>
+      <c r="D4">
+        <v>72.215599999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>59.997399999999999</v>
+      </c>
+      <c r="D5">
+        <v>58.849600000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E27DB59-CC7B-4BA0-B3F8-3C1105C01C74}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -623,6 +702,14 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documents/TAN measurements compilation.xlsx
+++ b/Documents/TAN measurements compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ACD576-F557-4362-925C-DF0E1113E997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D28266-28AF-47DD-9D6B-0436EF01DA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
   </bookViews>
@@ -593,15 +593,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB39E3B-1647-40FA-8E29-C72F98988571}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -614,8 +614,12 @@
       <c r="D2">
         <v>60.198399999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <f>AVERAGE(C2:D2)</f>
+        <v>59.477199999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>12</v>
       </c>
@@ -628,8 +632,12 @@
       <c r="D3">
         <v>62.852820000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <f t="shared" ref="E3:E5" si="0">AVERAGE(C3:D3)</f>
+        <v>64.096689999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>22</v>
       </c>
@@ -642,19 +650,49 @@
       <c r="D4">
         <v>72.215599999999995</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>71.521549999999991</v>
+      </c>
+      <c r="F4">
+        <f>AVERAGE(E4:E5)</f>
+        <v>70.476699999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>70.171400000000006</v>
+      </c>
+      <c r="D5">
+        <v>68.692300000000003</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>69.431849999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>28</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>59.997399999999999</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>58.849600000000002</v>
+      </c>
+      <c r="E6">
+        <f>AVERAGE(C6:D6)</f>
+        <v>59.423500000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/TAN measurements compilation.xlsx
+++ b/Documents/TAN measurements compilation.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Notes\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D28266-28AF-47DD-9D6B-0436EF01DA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2AFB3E-948C-444C-88A8-7B8954933360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{F3B8C5DB-CDB0-4011-A519-2C7BE5526A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Timesheet" sheetId="2" r:id="rId3"/>
+    <sheet name="FYP today" sheetId="4" r:id="rId3"/>
+    <sheet name="Timesheet" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Samples</t>
   </si>
@@ -68,6 +69,33 @@
   </si>
   <si>
     <t>sample</t>
+  </si>
+  <si>
+    <t>Ethanol loading (wt% wrt oil)</t>
+  </si>
+  <si>
+    <t>Catalyst</t>
+  </si>
+  <si>
+    <t>H2SO4</t>
+  </si>
+  <si>
+    <t>Amberlyst-36</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>Duration (h)</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Resulting TAN</t>
+  </si>
+  <si>
+    <t>error</t>
   </si>
 </sst>
 </file>
@@ -701,6 +729,103 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8302FFAE-7352-426E-B807-D0031949D91A}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>70</v>
+      </c>
+      <c r="E2">
+        <v>40</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>66.5</v>
+      </c>
+      <c r="F3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>62.2</v>
+      </c>
+      <c r="F4">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E27DB59-CC7B-4BA0-B3F8-3C1105C01C74}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
